--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="5760" yWindow="348" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="C-9-12" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="C-9-12" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hoja1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="ACOMETIDA">#REF!</definedName>
@@ -2586,7 +2586,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
@@ -2604,24 +2604,24 @@
       <nvPicPr>
         <cNvPr id="6" name="Imagen 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="555189" y="327972"/>
           <a:ext cx="1806529" cy="1723429"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2645,24 +2645,24 @@
       <nvPicPr>
         <cNvPr id="7" name="Picture 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="12628684" y="363359"/>
           <a:ext cx="2670669" cy="1876779"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5916,7 +5916,7 @@
       <c r="K123" s="208" t="n"/>
       <c r="L123" s="174" t="inlineStr">
         <is>
-          <t>Arq. Melissa Alvarenga</t>
+          <t>ARQ. MELISSA ALVARENGA</t>
         </is>
       </c>
       <c r="N123" s="208" t="n"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
@@ -4666,7 +4666,7 @@
       <c r="H63" s="129" t="n"/>
       <c r="I63" s="253" t="n"/>
       <c r="J63" s="196" t="n"/>
-      <c r="K63" s="202" t="n"/>
+      <c r="K63" s="253" t="n"/>
       <c r="L63" s="196" t="n"/>
       <c r="M63" s="222" t="n"/>
       <c r="N63" s="129" t="n"/>
@@ -4688,7 +4688,7 @@
       <c r="H64" s="129" t="n"/>
       <c r="I64" s="251" t="n"/>
       <c r="J64" s="196" t="n"/>
-      <c r="K64" s="195" t="n"/>
+      <c r="K64" s="251" t="n"/>
       <c r="L64" s="196" t="n"/>
       <c r="M64" s="209" t="n"/>
       <c r="N64" s="129" t="n"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
@@ -90,7 +90,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;Q&quot;* #,##0.00_-;\-&quot;Q&quot;* #,##0.00_-;_-&quot;Q&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -313,6 +313,11 @@
       <color rgb="FF001545"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Open Sans"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1374,7 +1379,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="359">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2507,6 +2512,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="89" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5929,22 +5937,14 @@
       <c r="Q123" s="55" t="n"/>
       <c r="R123" s="55" t="n"/>
     </row>
-    <row r="124" customFormat="1" s="123">
+    <row r="124" ht="27.6" customFormat="1" customHeight="1" s="123">
       <c r="B124" s="74" t="n"/>
       <c r="C124" s="74" t="n"/>
-      <c r="D124" s="55" t="n"/>
-      <c r="E124" s="55" t="n"/>
-      <c r="F124" s="55" t="n"/>
-      <c r="G124" s="55" t="n"/>
-      <c r="H124" s="55" t="n"/>
-      <c r="I124" s="55" t="n"/>
-      <c r="J124" s="55" t="n"/>
-      <c r="K124" s="55" t="n"/>
-      <c r="L124" s="77" t="n"/>
-      <c r="M124" s="77" t="n"/>
-      <c r="N124" s="55" t="n"/>
-      <c r="O124" s="77" t="n"/>
-      <c r="P124" s="78" t="n"/>
+      <c r="D124" s="359" t="inlineStr">
+        <is>
+          <t>{{TIPO_CONTRATO_MENSAJE}}</t>
+        </is>
+      </c>
       <c r="Q124" s="55" t="n"/>
       <c r="R124" s="55" t="n"/>
     </row>
@@ -5972,7 +5972,7 @@
       <c r="R126" s="55" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="197">
+  <mergeCells count="198">
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="H123:J123"/>
     <mergeCell ref="D116:F116"/>
@@ -6051,6 +6051,7 @@
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="G65:H65"/>
     <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D124:P124"/>
     <mergeCell ref="D44:I44"/>
     <mergeCell ref="O123:P123"/>
     <mergeCell ref="D27:J27"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
@@ -1379,7 +1379,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="361">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2514,6 +2514,9 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2981,7 +2984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:W126"/>
+  <dimension ref="A1:W126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.4"/>
   <cols>
     <col width="3.109375" customWidth="1" style="148" min="1" max="1"/>
@@ -3006,6 +3009,7 @@
     <col width="11.44140625" customWidth="1" style="148" min="22" max="16384"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="306" t="n"/>
       <c r="C2" s="306" t="n"/>
@@ -5940,7 +5944,7 @@
     <row r="124" ht="27.6" customFormat="1" customHeight="1" s="123">
       <c r="B124" s="74" t="n"/>
       <c r="C124" s="74" t="n"/>
-      <c r="D124" s="359" t="inlineStr">
+      <c r="D124" s="360" t="inlineStr">
         <is>
           <t>{{TIPO_CONTRATO_MENSAJE}}</t>
         </is>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA_REFORMA.xlsx
@@ -79,7 +79,7 @@
     <definedName name="DUCELEC" localSheetId="0">#REF!</definedName>
     <definedName name="ESPECIALES" localSheetId="0">#REF!</definedName>
     <definedName name="EXP" localSheetId="0">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$125</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$136</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -319,7 +319,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -384,8 +384,13 @@
         <fgColor rgb="FF001545"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="90">
+  <borders count="92">
     <border>
       <left/>
       <right/>
@@ -1374,12 +1379,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="361">
+  <cellXfs count="383">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -2518,6 +2543,88 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="90" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="91" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="91" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="91" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="90" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="91" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="91" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="91" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="49" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="64" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="51" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="47" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="47" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="61" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2984,7 +3091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W126"/>
+  <dimension ref="A1:W135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.4"/>
   <cols>
     <col width="3.109375" customWidth="1" style="148" min="1" max="1"/>
@@ -3309,7 +3416,7 @@
       <c r="C14" s="59" t="n"/>
       <c r="D14" s="327" t="inlineStr">
         <is>
-          <t>NO. TELEFONO:</t>
+          <t>NO. TELÉFONO:</t>
         </is>
       </c>
       <c r="E14" s="145" t="n"/>
@@ -3379,7 +3486,7 @@
       <c r="C16" s="59" t="n"/>
       <c r="D16" s="328" t="inlineStr">
         <is>
-          <t>NO. COTIZACION</t>
+          <t>NO. COTIZACIÓN</t>
         </is>
       </c>
       <c r="E16" s="269" t="n"/>
@@ -3443,7 +3550,7 @@
       <c r="K18" s="73" t="n"/>
       <c r="L18" s="330" t="inlineStr">
         <is>
-          <t>TIEMPOS DE PAGO CON RECEPCION DE FACTURA</t>
+          <t>TIEMPOS DE PAGO CON RECEPCIÓN DE FACTURA</t>
         </is>
       </c>
       <c r="M18" s="138" t="n"/>
@@ -3483,7 +3590,7 @@
       <c r="O19" s="139" t="n"/>
       <c r="P19" s="84" t="inlineStr">
         <is>
-          <t>15 DIAS</t>
+          <t>15 DÍAS</t>
         </is>
       </c>
       <c r="Q19" s="55" t="n"/>
@@ -3494,7 +3601,7 @@
       <c r="C20" s="74" t="n"/>
       <c r="D20" s="221" t="inlineStr">
         <is>
-          <t>Punto de acta firmado por contratista, genrete E4, lider E4</t>
+          <t>Punto de acta firmado por contratista, gerente E4, líder E4</t>
         </is>
       </c>
       <c r="E20" s="126" t="n"/>
@@ -3518,7 +3625,7 @@
       <c r="O20" s="139" t="n"/>
       <c r="P20" s="85" t="inlineStr">
         <is>
-          <t>30 DIAS</t>
+          <t>30 DÍAS</t>
         </is>
       </c>
       <c r="Q20" s="55" t="n"/>
@@ -3538,7 +3645,7 @@
       <c r="H21" s="127" t="n"/>
       <c r="I21" s="146" t="inlineStr">
         <is>
-          <t>anticipo / estimacion</t>
+          <t>anticipo / estimación</t>
         </is>
       </c>
       <c r="J21" s="126" t="n"/>
@@ -3553,7 +3660,7 @@
       <c r="O21" s="139" t="n"/>
       <c r="P21" s="84" t="inlineStr">
         <is>
-          <t>30 DIAS</t>
+          <t>30 DÍAS</t>
         </is>
       </c>
       <c r="Q21" s="55" t="n"/>
@@ -3608,7 +3715,7 @@
       <c r="H23" s="127" t="n"/>
       <c r="I23" s="146" t="inlineStr">
         <is>
-          <t>para estimacion</t>
+          <t>para estimación</t>
         </is>
       </c>
       <c r="J23" s="126" t="n"/>
@@ -3626,7 +3733,7 @@
       <c r="C24" s="74" t="n"/>
       <c r="D24" s="221" t="inlineStr">
         <is>
-          <t>Carta de garantia</t>
+          <t>Carta de garantía</t>
         </is>
       </c>
       <c r="E24" s="126" t="n"/>
@@ -3681,7 +3788,8 @@
       <c r="O25" s="139" t="n"/>
       <c r="P25" s="84" t="inlineStr">
         <is>
-          <t>Lunes de               8:00 AM- 4:00 PM</t>
+          <t>Lunes de
+8:00 AM a 4:00 PM</t>
         </is>
       </c>
       <c r="Q25" s="55" t="n"/>
@@ -3692,7 +3800,7 @@
       <c r="C26" s="74" t="n"/>
       <c r="D26" s="331" t="inlineStr">
         <is>
-          <t>TODO DOCUMENTO DE ESTIMACION Y ADELANTO DEBE IR FIRMADO POR EL CONTRATISTA</t>
+          <t>TODO DOCUMENTO DE ESTIMACIÓN Y ADELANTO DEBE IR FIRMADO POR EL CONTRATISTA</t>
         </is>
       </c>
       <c r="E26" s="138" t="n"/>
@@ -3712,7 +3820,8 @@
       <c r="O26" s="139" t="n"/>
       <c r="P26" s="85" t="inlineStr">
         <is>
-          <t>Lunes y Martes de 8:00 AM- 4:00 PM</t>
+          <t>Lunes y Martes de
+8:00 AM a 4:00 PM</t>
         </is>
       </c>
       <c r="Q26" s="55" t="n"/>
@@ -3739,7 +3848,8 @@
       <c r="O27" s="139" t="n"/>
       <c r="P27" s="84" t="inlineStr">
         <is>
-          <t>Lunes de               8:00 AM- 4:00 PM</t>
+          <t>Lunes de
+8:00 AM a 4:00 PM</t>
         </is>
       </c>
       <c r="Q27" s="333" t="n"/>
@@ -3819,7 +3929,7 @@
       <c r="O30" s="180" t="n"/>
       <c r="P30" s="9" t="inlineStr">
         <is>
-          <t>1% POR DIA</t>
+          <t>1% POR DÍA</t>
         </is>
       </c>
       <c r="Q30" s="55" t="n"/>
@@ -3900,7 +4010,7 @@
       <c r="C33" s="74" t="n"/>
       <c r="D33" s="124" t="inlineStr">
         <is>
-          <t>Reunión semanal con LIDER DE PROYECTO</t>
+          <t>Reunión semanal con LÍDER DE PROYECTO</t>
         </is>
       </c>
       <c r="E33" s="120" t="n"/>
@@ -3916,7 +4026,7 @@
       <c r="K33" s="55" t="n"/>
       <c r="L33" s="248" t="inlineStr">
         <is>
-          <t>Por no cumplir con documentos de reporteria semanal</t>
+          <t>Por no cumplir con documentos de reportería semanal</t>
         </is>
       </c>
       <c r="M33" s="182" t="n"/>
@@ -3978,7 +4088,7 @@
       <c r="K35" s="55" t="n"/>
       <c r="L35" s="335" t="inlineStr">
         <is>
-          <t>DOCUMENTO ENTREGADOS A CONTRATISTA POR PARTE DE E4</t>
+          <t>DOCUMENTOS ENTREGADOS A CONTRATISTA POR PARTE DE E4</t>
         </is>
       </c>
       <c r="Q35" s="55" t="n"/>
@@ -4027,7 +4137,7 @@
       <c r="K37" s="55" t="n"/>
       <c r="L37" s="221" t="inlineStr">
         <is>
-          <t>Politica de recepcion de facturas y pagos</t>
+          <t>Política de recepción de facturas y pagos</t>
         </is>
       </c>
       <c r="M37" s="126" t="n"/>
@@ -4062,7 +4172,7 @@
       <c r="K38" s="55" t="n"/>
       <c r="L38" s="125" t="inlineStr">
         <is>
-          <t>Politica de SSO en obra</t>
+          <t>Política de SSO en obra</t>
         </is>
       </c>
       <c r="M38" s="126" t="n"/>
@@ -4365,7 +4475,7 @@
       </c>
       <c r="E49" s="337" t="inlineStr">
         <is>
-          <t>DESCRIPCION</t>
+          <t>DESCRIPCIÓN</t>
         </is>
       </c>
       <c r="K49" s="337" t="inlineStr">
@@ -4400,102 +4510,102 @@
     <row r="50" ht="69.90000000000001" customHeight="1">
       <c r="B50" s="8" t="n"/>
       <c r="C50" s="23" t="n"/>
-      <c r="D50" s="293" t="n"/>
-      <c r="E50" s="247" t="n"/>
+      <c r="D50" s="361" t="n"/>
+      <c r="E50" s="362" t="n"/>
       <c r="F50" s="161" t="n"/>
       <c r="G50" s="161" t="n"/>
       <c r="H50" s="161" t="n"/>
       <c r="I50" s="161" t="n"/>
-      <c r="J50" s="133" t="n"/>
+      <c r="J50" s="363" t="n"/>
       <c r="K50" s="26" t="n"/>
-      <c r="L50" s="27" t="n"/>
+      <c r="L50" s="364" t="n"/>
       <c r="M50" s="28" t="n"/>
-      <c r="N50" s="184" t="n"/>
-      <c r="O50" s="133" t="n"/>
+      <c r="N50" s="365" t="n"/>
+      <c r="O50" s="363" t="n"/>
       <c r="P50" s="29" t="n"/>
     </row>
     <row r="51" ht="68.09999999999999" customHeight="1">
       <c r="B51" s="8" t="n"/>
       <c r="C51" s="23" t="n"/>
-      <c r="D51" s="294" t="n"/>
-      <c r="E51" s="178" t="n"/>
+      <c r="D51" s="366" t="n"/>
+      <c r="E51" s="367" t="n"/>
       <c r="F51" s="161" t="n"/>
       <c r="G51" s="161" t="n"/>
       <c r="H51" s="161" t="n"/>
       <c r="I51" s="161" t="n"/>
-      <c r="J51" s="133" t="n"/>
+      <c r="J51" s="363" t="n"/>
       <c r="K51" s="31" t="n"/>
-      <c r="L51" s="32" t="n"/>
+      <c r="L51" s="368" t="n"/>
       <c r="M51" s="33" t="n"/>
-      <c r="N51" s="132" t="n"/>
-      <c r="O51" s="133" t="n"/>
+      <c r="N51" s="369" t="n"/>
+      <c r="O51" s="363" t="n"/>
       <c r="P51" s="34" t="n"/>
     </row>
     <row r="52" ht="68.09999999999999" customHeight="1">
       <c r="B52" s="8" t="n"/>
       <c r="C52" s="23" t="n"/>
-      <c r="D52" s="293" t="n"/>
-      <c r="E52" s="247" t="n"/>
+      <c r="D52" s="361" t="n"/>
+      <c r="E52" s="362" t="n"/>
       <c r="F52" s="161" t="n"/>
       <c r="G52" s="161" t="n"/>
       <c r="H52" s="161" t="n"/>
       <c r="I52" s="161" t="n"/>
-      <c r="J52" s="133" t="n"/>
+      <c r="J52" s="363" t="n"/>
       <c r="K52" s="26" t="n"/>
-      <c r="L52" s="27" t="n"/>
+      <c r="L52" s="364" t="n"/>
       <c r="M52" s="28" t="n"/>
-      <c r="N52" s="184" t="n"/>
-      <c r="O52" s="133" t="n"/>
+      <c r="N52" s="365" t="n"/>
+      <c r="O52" s="363" t="n"/>
       <c r="P52" s="29" t="n"/>
     </row>
     <row r="53" ht="69.90000000000001" customHeight="1">
       <c r="B53" s="8" t="n"/>
       <c r="C53" s="23" t="n"/>
-      <c r="D53" s="294" t="n"/>
-      <c r="E53" s="178" t="n"/>
+      <c r="D53" s="366" t="n"/>
+      <c r="E53" s="367" t="n"/>
       <c r="F53" s="161" t="n"/>
       <c r="G53" s="161" t="n"/>
       <c r="H53" s="161" t="n"/>
       <c r="I53" s="161" t="n"/>
-      <c r="J53" s="133" t="n"/>
+      <c r="J53" s="363" t="n"/>
       <c r="K53" s="31" t="n"/>
-      <c r="L53" s="32" t="n"/>
+      <c r="L53" s="368" t="n"/>
       <c r="M53" s="33" t="n"/>
-      <c r="N53" s="132" t="n"/>
-      <c r="O53" s="133" t="n"/>
+      <c r="N53" s="369" t="n"/>
+      <c r="O53" s="363" t="n"/>
       <c r="P53" s="34" t="n"/>
     </row>
     <row r="54" ht="69.90000000000001" customHeight="1">
       <c r="B54" s="23" t="n"/>
-      <c r="D54" s="293" t="n"/>
-      <c r="E54" s="247" t="n"/>
+      <c r="D54" s="361" t="n"/>
+      <c r="E54" s="362" t="n"/>
       <c r="F54" s="161" t="n"/>
       <c r="G54" s="161" t="n"/>
       <c r="H54" s="161" t="n"/>
       <c r="I54" s="161" t="n"/>
-      <c r="J54" s="133" t="n"/>
+      <c r="J54" s="363" t="n"/>
       <c r="K54" s="26" t="n"/>
-      <c r="L54" s="27" t="n"/>
+      <c r="L54" s="364" t="n"/>
       <c r="M54" s="28" t="n"/>
-      <c r="N54" s="184" t="n"/>
-      <c r="O54" s="133" t="n"/>
+      <c r="N54" s="365" t="n"/>
+      <c r="O54" s="363" t="n"/>
       <c r="P54" s="29" t="n"/>
     </row>
     <row r="55" ht="66.90000000000001" customHeight="1">
       <c r="B55" s="8" t="n"/>
       <c r="C55" s="23" t="n"/>
-      <c r="D55" s="294" t="n"/>
-      <c r="E55" s="178" t="n"/>
+      <c r="D55" s="366" t="n"/>
+      <c r="E55" s="367" t="n"/>
       <c r="F55" s="161" t="n"/>
       <c r="G55" s="161" t="n"/>
       <c r="H55" s="161" t="n"/>
       <c r="I55" s="161" t="n"/>
-      <c r="J55" s="133" t="n"/>
+      <c r="J55" s="363" t="n"/>
       <c r="K55" s="31" t="n"/>
-      <c r="L55" s="32" t="n"/>
+      <c r="L55" s="368" t="n"/>
       <c r="M55" s="33" t="n"/>
-      <c r="N55" s="132" t="n"/>
-      <c r="O55" s="133" t="n"/>
+      <c r="N55" s="369" t="n"/>
+      <c r="O55" s="363" t="n"/>
       <c r="P55" s="34" t="n"/>
     </row>
     <row r="56" ht="21.9" customHeight="1">
@@ -4624,7 +4734,7 @@
       <c r="J61" s="194" t="n"/>
       <c r="K61" s="344" t="inlineStr">
         <is>
-          <t>DIAS</t>
+          <t>DÍAS</t>
         </is>
       </c>
       <c r="L61" s="118" t="n"/>
@@ -4671,16 +4781,16 @@
     <row r="63" ht="21" customHeight="1">
       <c r="B63" s="74" t="n"/>
       <c r="C63" s="74" t="n"/>
-      <c r="D63" s="276" t="n"/>
+      <c r="D63" s="370" t="n"/>
       <c r="E63" s="129" t="n"/>
       <c r="F63" s="130" t="n"/>
-      <c r="G63" s="210" t="n"/>
+      <c r="G63" s="371" t="n"/>
       <c r="H63" s="129" t="n"/>
-      <c r="I63" s="253" t="n"/>
+      <c r="I63" s="372" t="n"/>
       <c r="J63" s="196" t="n"/>
-      <c r="K63" s="253" t="n"/>
+      <c r="K63" s="372" t="n"/>
       <c r="L63" s="196" t="n"/>
-      <c r="M63" s="222" t="n"/>
+      <c r="M63" s="373" t="n"/>
       <c r="N63" s="129" t="n"/>
       <c r="O63" s="129" t="n"/>
       <c r="P63" s="130" t="n"/>
@@ -4715,16 +4825,16 @@
     <row r="65" ht="20.4" customFormat="1" customHeight="1" s="123">
       <c r="B65" s="74" t="n"/>
       <c r="C65" s="74" t="n"/>
-      <c r="D65" s="131" t="n"/>
+      <c r="D65" s="374" t="n"/>
       <c r="E65" s="129" t="n"/>
       <c r="F65" s="130" t="n"/>
-      <c r="G65" s="210" t="n"/>
+      <c r="G65" s="371" t="n"/>
       <c r="H65" s="129" t="n"/>
-      <c r="I65" s="253" t="n"/>
+      <c r="I65" s="372" t="n"/>
       <c r="J65" s="196" t="n"/>
-      <c r="K65" s="253" t="n"/>
+      <c r="K65" s="372" t="n"/>
       <c r="L65" s="196" t="n"/>
-      <c r="M65" s="222" t="n"/>
+      <c r="M65" s="373" t="n"/>
       <c r="N65" s="129" t="n"/>
       <c r="O65" s="129" t="n"/>
       <c r="P65" s="130" t="n"/>
@@ -4824,10 +4934,10 @@
     <row r="70" ht="25.8" customHeight="1">
       <c r="B70" s="74" t="n"/>
       <c r="C70" s="74" t="n"/>
-      <c r="D70" s="110" t="n">
+      <c r="D70" s="375" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="303" t="n"/>
+      <c r="E70" s="376" t="n"/>
       <c r="F70" s="187" t="n"/>
       <c r="G70" s="187" t="n"/>
       <c r="H70" s="187" t="n"/>
@@ -4864,10 +4974,10 @@
     <row r="72" ht="24.9" customHeight="1">
       <c r="B72" s="8" t="n"/>
       <c r="C72" s="8" t="n"/>
-      <c r="D72" s="110" t="n">
+      <c r="D72" s="375" t="n">
         <v>4</v>
       </c>
-      <c r="E72" s="207" t="n"/>
+      <c r="E72" s="377" t="n"/>
       <c r="F72" s="129" t="n"/>
       <c r="G72" s="129" t="n"/>
       <c r="H72" s="129" t="n"/>
@@ -4926,7 +5036,7 @@
       </c>
       <c r="E75" s="347" t="inlineStr">
         <is>
-          <t>SERVICIOS BASICOS NECESARIOS PARA TRABAJAR</t>
+          <t>SERVICIOS BÁSICOS NECESARIOS PARA TRABAJAR</t>
         </is>
       </c>
       <c r="F75" s="117" t="n"/>
@@ -4971,10 +5081,10 @@
     <row r="77" ht="24.9" customHeight="1">
       <c r="B77" s="74" t="n"/>
       <c r="C77" s="74" t="n"/>
-      <c r="D77" s="110" t="n">
+      <c r="D77" s="375" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="305" t="n"/>
+      <c r="E77" s="378" t="n"/>
       <c r="F77" s="187" t="n"/>
       <c r="G77" s="187" t="n"/>
       <c r="H77" s="187" t="n"/>
@@ -5013,10 +5123,10 @@
     <row r="79" ht="27" customHeight="1">
       <c r="B79" s="8" t="n"/>
       <c r="C79" s="8" t="n"/>
-      <c r="D79" s="110" t="n">
+      <c r="D79" s="375" t="n">
         <v>4</v>
       </c>
-      <c r="E79" s="254" t="n"/>
+      <c r="E79" s="379" t="n"/>
       <c r="F79" s="129" t="n"/>
       <c r="G79" s="129" t="n"/>
       <c r="H79" s="129" t="n"/>
@@ -5128,10 +5238,10 @@
     <row r="85" ht="26.4" customHeight="1">
       <c r="B85" s="8" t="n"/>
       <c r="C85" s="8" t="n"/>
-      <c r="D85" s="155" t="n">
+      <c r="D85" s="380" t="n">
         <v>2</v>
       </c>
-      <c r="E85" s="301" t="n"/>
+      <c r="E85" s="381" t="n"/>
       <c r="F85" s="156" t="n"/>
       <c r="G85" s="156" t="n"/>
       <c r="H85" s="156" t="n"/>
@@ -5167,7 +5277,7 @@
       <c r="N86" s="4" t="n"/>
       <c r="O86" s="242" t="inlineStr">
         <is>
-          <t>Cartas firmadas por Lider de Proyecto y Maestro de obras, con fotografias de avance, cuadro de cantidades y renglones</t>
+          <t>Cartas firmadas por Líder de Proyecto y Maestro de obras, con fotografías de avance, cuadro de cantidades y renglones</t>
         </is>
       </c>
       <c r="Q86" s="44" t="n"/>
@@ -5181,10 +5291,10 @@
     <row r="87" ht="26.4" customHeight="1">
       <c r="B87" s="8" t="n"/>
       <c r="C87" s="8" t="n"/>
-      <c r="D87" s="155" t="n">
+      <c r="D87" s="380" t="n">
         <v>4</v>
       </c>
-      <c r="E87" s="134" t="n"/>
+      <c r="E87" s="382" t="n"/>
       <c r="F87" s="135" t="n"/>
       <c r="G87" s="135" t="n"/>
       <c r="H87" s="135" t="n"/>
@@ -5219,10 +5329,10 @@
     <row r="89" ht="27.6" customHeight="1">
       <c r="B89" s="8" t="n"/>
       <c r="C89" s="8" t="n"/>
-      <c r="D89" s="155" t="n">
+      <c r="D89" s="380" t="n">
         <v>6</v>
       </c>
-      <c r="E89" s="134" t="n"/>
+      <c r="E89" s="382" t="n"/>
       <c r="F89" s="135" t="n"/>
       <c r="G89" s="135" t="n"/>
       <c r="H89" s="135" t="n"/>
@@ -5261,10 +5371,10 @@
     <row r="91" ht="27.6" customHeight="1">
       <c r="B91" s="8" t="n"/>
       <c r="C91" s="8" t="n"/>
-      <c r="D91" s="155" t="n">
+      <c r="D91" s="380" t="n">
         <v>8</v>
       </c>
-      <c r="E91" s="134" t="n"/>
+      <c r="E91" s="382" t="n"/>
       <c r="F91" s="135" t="n"/>
       <c r="G91" s="135" t="n"/>
       <c r="H91" s="135" t="n"/>
@@ -5306,10 +5416,10 @@
     <row r="93" ht="27.6" customHeight="1">
       <c r="B93" s="8" t="n"/>
       <c r="C93" s="8" t="n"/>
-      <c r="D93" s="155" t="n">
+      <c r="D93" s="380" t="n">
         <v>10</v>
       </c>
-      <c r="E93" s="134" t="n"/>
+      <c r="E93" s="382" t="n"/>
       <c r="F93" s="135" t="n"/>
       <c r="G93" s="135" t="n"/>
       <c r="H93" s="135" t="n"/>
@@ -5321,7 +5431,7 @@
       <c r="N93" s="5" t="n"/>
       <c r="O93" s="242" t="inlineStr">
         <is>
-          <t>Contratista es el unico responsable de cumplir con los pagos directo a su personal en obra, tanto salario pactado como prestaciones en dado apliquen, quitando responsabilidad a E4 ante cualquier inconveniente</t>
+          <t>Contratista es el único responsable de cumplir con los pagos directo a su personal en obra, tanto salario pactado como prestaciones en dado caso apliquen, quitando responsabilidad a E4 ante cualquier inconveniente</t>
         </is>
       </c>
       <c r="Q93" s="44" t="n"/>
@@ -5349,10 +5459,10 @@
     <row r="95" ht="27.6" customHeight="1">
       <c r="B95" s="8" t="n"/>
       <c r="C95" s="8" t="n"/>
-      <c r="D95" s="155" t="n">
+      <c r="D95" s="380" t="n">
         <v>12</v>
       </c>
-      <c r="E95" s="134" t="n"/>
+      <c r="E95" s="382" t="n"/>
       <c r="F95" s="135" t="n"/>
       <c r="G95" s="135" t="n"/>
       <c r="H95" s="135" t="n"/>
@@ -5387,10 +5497,10 @@
     <row r="97" ht="27.6" customHeight="1">
       <c r="B97" s="8" t="n"/>
       <c r="C97" s="8" t="n"/>
-      <c r="D97" s="155" t="n">
+      <c r="D97" s="380" t="n">
         <v>14</v>
       </c>
-      <c r="E97" s="134" t="n"/>
+      <c r="E97" s="382" t="n"/>
       <c r="F97" s="135" t="n"/>
       <c r="G97" s="135" t="n"/>
       <c r="H97" s="135" t="n"/>
@@ -5429,10 +5539,10 @@
     <row r="99" ht="27.6" customHeight="1">
       <c r="B99" s="8" t="n"/>
       <c r="C99" s="8" t="n"/>
-      <c r="D99" s="155" t="n">
+      <c r="D99" s="380" t="n">
         <v>16</v>
       </c>
-      <c r="E99" s="134" t="n"/>
+      <c r="E99" s="382" t="n"/>
       <c r="F99" s="135" t="n"/>
       <c r="G99" s="135" t="n"/>
       <c r="H99" s="135" t="n"/>
@@ -5477,10 +5587,10 @@
     <row r="101" ht="27.6" customHeight="1">
       <c r="B101" s="8" t="n"/>
       <c r="C101" s="8" t="n"/>
-      <c r="D101" s="155" t="n">
+      <c r="D101" s="380" t="n">
         <v>18</v>
       </c>
-      <c r="E101" s="134" t="n"/>
+      <c r="E101" s="382" t="n"/>
       <c r="F101" s="135" t="n"/>
       <c r="G101" s="135" t="n"/>
       <c r="H101" s="135" t="n"/>
@@ -5515,10 +5625,10 @@
     <row r="103" ht="27.6" customHeight="1">
       <c r="B103" s="8" t="n"/>
       <c r="C103" s="8" t="n"/>
-      <c r="D103" s="155" t="n">
+      <c r="D103" s="380" t="n">
         <v>20</v>
       </c>
-      <c r="E103" s="134" t="n"/>
+      <c r="E103" s="382" t="n"/>
       <c r="F103" s="135" t="n"/>
       <c r="G103" s="135" t="n"/>
       <c r="H103" s="135" t="n"/>
@@ -5553,10 +5663,10 @@
     <row r="105" ht="27.6" customHeight="1">
       <c r="B105" s="8" t="n"/>
       <c r="C105" s="8" t="n"/>
-      <c r="D105" s="155" t="n">
+      <c r="D105" s="380" t="n">
         <v>22</v>
       </c>
-      <c r="E105" s="134" t="n"/>
+      <c r="E105" s="382" t="n"/>
       <c r="F105" s="135" t="n"/>
       <c r="G105" s="135" t="n"/>
       <c r="H105" s="135" t="n"/>
@@ -5595,10 +5705,10 @@
     <row r="107" ht="27.6" customHeight="1">
       <c r="B107" s="8" t="n"/>
       <c r="C107" s="8" t="n"/>
-      <c r="D107" s="155" t="n">
+      <c r="D107" s="380" t="n">
         <v>24</v>
       </c>
-      <c r="E107" s="134" t="n"/>
+      <c r="E107" s="382" t="n"/>
       <c r="F107" s="135" t="n"/>
       <c r="G107" s="135" t="n"/>
       <c r="H107" s="135" t="n"/>
@@ -5633,10 +5743,10 @@
     <row r="109" ht="27.6" customHeight="1">
       <c r="B109" s="8" t="n"/>
       <c r="C109" s="8" t="n"/>
-      <c r="D109" s="155" t="n">
+      <c r="D109" s="380" t="n">
         <v>26</v>
       </c>
-      <c r="E109" s="134" t="n"/>
+      <c r="E109" s="382" t="n"/>
       <c r="F109" s="135" t="n"/>
       <c r="G109" s="135" t="n"/>
       <c r="H109" s="135" t="n"/>
@@ -5671,10 +5781,10 @@
     <row r="111" ht="27.6" customHeight="1" thickBot="1">
       <c r="B111" s="8" t="n"/>
       <c r="C111" s="8" t="n"/>
-      <c r="D111" s="155" t="n">
+      <c r="D111" s="380" t="n">
         <v>28</v>
       </c>
-      <c r="E111" s="134" t="n"/>
+      <c r="E111" s="382" t="n"/>
       <c r="F111" s="135" t="n"/>
       <c r="G111" s="135" t="n"/>
       <c r="H111" s="135" t="n"/>
@@ -5736,7 +5846,7 @@
       <c r="C114" s="74" t="n"/>
       <c r="D114" s="317" t="inlineStr">
         <is>
-          <t>AREA DE FIRMAS</t>
+          <t>ÁREA DE FIRMAS</t>
         </is>
       </c>
       <c r="Q114" s="55" t="n"/>
@@ -5971,12 +6081,207 @@
       <c r="Q125" s="55" t="n"/>
       <c r="R125" s="55" t="n"/>
     </row>
-    <row r="126">
+    <row r="126" ht="18" customHeight="1">
       <c r="Q126" s="55" t="n"/>
       <c r="R126" s="55" t="n"/>
     </row>
+    <row r="127" ht="24.9" customHeight="1">
+      <c r="B127" s="74" t="n"/>
+      <c r="C127" s="74" t="n"/>
+      <c r="D127" s="341" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="E127" s="345" t="inlineStr">
+        <is>
+          <t>ANEXOS: DOCUMENTOS ADJUNTOS A LA SOLICITUD</t>
+        </is>
+      </c>
+      <c r="F127" s="117" t="n"/>
+      <c r="G127" s="117" t="n"/>
+      <c r="H127" s="117" t="n"/>
+      <c r="I127" s="117" t="n"/>
+      <c r="J127" s="117" t="n"/>
+      <c r="K127" s="117" t="n"/>
+      <c r="L127" s="117" t="n"/>
+      <c r="M127" s="117" t="n"/>
+      <c r="N127" s="117" t="n"/>
+      <c r="O127" s="117" t="n"/>
+      <c r="P127" s="118" t="n"/>
+      <c r="Q127" s="55" t="n"/>
+      <c r="R127" s="55" t="n"/>
+    </row>
+    <row r="128" ht="24.9" customHeight="1">
+      <c r="B128" s="74" t="n"/>
+      <c r="C128" s="99" t="n"/>
+      <c r="D128" s="108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="302" t="n"/>
+      <c r="F128" s="187" t="n"/>
+      <c r="G128" s="187" t="n"/>
+      <c r="H128" s="187" t="n"/>
+      <c r="I128" s="187" t="n"/>
+      <c r="J128" s="187" t="n"/>
+      <c r="K128" s="187" t="n"/>
+      <c r="L128" s="187" t="n"/>
+      <c r="M128" s="187" t="n"/>
+      <c r="N128" s="187" t="n"/>
+      <c r="O128" s="187" t="n"/>
+      <c r="P128" s="188" t="n"/>
+      <c r="Q128" s="99" t="n"/>
+      <c r="R128" s="99" t="n"/>
+    </row>
+    <row r="129" ht="25.8" customHeight="1">
+      <c r="B129" s="74" t="n"/>
+      <c r="C129" s="74" t="n"/>
+      <c r="D129" s="375" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" s="376" t="n"/>
+      <c r="F129" s="187" t="n"/>
+      <c r="G129" s="187" t="n"/>
+      <c r="H129" s="187" t="n"/>
+      <c r="I129" s="187" t="n"/>
+      <c r="J129" s="187" t="n"/>
+      <c r="K129" s="187" t="n"/>
+      <c r="L129" s="187" t="n"/>
+      <c r="M129" s="187" t="n"/>
+      <c r="N129" s="187" t="n"/>
+      <c r="O129" s="187" t="n"/>
+      <c r="P129" s="188" t="n"/>
+      <c r="Q129" s="55" t="n"/>
+      <c r="R129" s="55" t="n"/>
+    </row>
+    <row r="130" ht="24.9" customHeight="1">
+      <c r="B130" s="74" t="n"/>
+      <c r="C130" s="99" t="n"/>
+      <c r="D130" s="108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" s="302" t="n"/>
+      <c r="F130" s="187" t="n"/>
+      <c r="G130" s="187" t="n"/>
+      <c r="H130" s="187" t="n"/>
+      <c r="I130" s="187" t="n"/>
+      <c r="J130" s="187" t="n"/>
+      <c r="K130" s="187" t="n"/>
+      <c r="L130" s="187" t="n"/>
+      <c r="M130" s="187" t="n"/>
+      <c r="N130" s="187" t="n"/>
+      <c r="O130" s="187" t="n"/>
+      <c r="P130" s="188" t="n"/>
+      <c r="Q130" s="99" t="n"/>
+      <c r="R130" s="99" t="n"/>
+    </row>
+    <row r="131" ht="25.8" customHeight="1">
+      <c r="B131" s="74" t="n"/>
+      <c r="C131" s="74" t="n"/>
+      <c r="D131" s="375" t="n">
+        <v>4</v>
+      </c>
+      <c r="E131" s="376" t="n"/>
+      <c r="F131" s="187" t="n"/>
+      <c r="G131" s="187" t="n"/>
+      <c r="H131" s="187" t="n"/>
+      <c r="I131" s="187" t="n"/>
+      <c r="J131" s="187" t="n"/>
+      <c r="K131" s="187" t="n"/>
+      <c r="L131" s="187" t="n"/>
+      <c r="M131" s="187" t="n"/>
+      <c r="N131" s="187" t="n"/>
+      <c r="O131" s="187" t="n"/>
+      <c r="P131" s="188" t="n"/>
+      <c r="Q131" s="55" t="n"/>
+      <c r="R131" s="55" t="n"/>
+    </row>
+    <row r="132" ht="24.9" customHeight="1">
+      <c r="B132" s="74" t="n"/>
+      <c r="C132" s="99" t="n"/>
+      <c r="D132" s="108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E132" s="302" t="n"/>
+      <c r="F132" s="187" t="n"/>
+      <c r="G132" s="187" t="n"/>
+      <c r="H132" s="187" t="n"/>
+      <c r="I132" s="187" t="n"/>
+      <c r="J132" s="187" t="n"/>
+      <c r="K132" s="187" t="n"/>
+      <c r="L132" s="187" t="n"/>
+      <c r="M132" s="187" t="n"/>
+      <c r="N132" s="187" t="n"/>
+      <c r="O132" s="187" t="n"/>
+      <c r="P132" s="188" t="n"/>
+      <c r="Q132" s="99" t="n"/>
+      <c r="R132" s="99" t="n"/>
+    </row>
+    <row r="133" ht="25.8" customHeight="1">
+      <c r="B133" s="74" t="n"/>
+      <c r="C133" s="74" t="n"/>
+      <c r="D133" s="375" t="n">
+        <v>6</v>
+      </c>
+      <c r="E133" s="376" t="n"/>
+      <c r="F133" s="187" t="n"/>
+      <c r="G133" s="187" t="n"/>
+      <c r="H133" s="187" t="n"/>
+      <c r="I133" s="187" t="n"/>
+      <c r="J133" s="187" t="n"/>
+      <c r="K133" s="187" t="n"/>
+      <c r="L133" s="187" t="n"/>
+      <c r="M133" s="187" t="n"/>
+      <c r="N133" s="187" t="n"/>
+      <c r="O133" s="187" t="n"/>
+      <c r="P133" s="188" t="n"/>
+      <c r="Q133" s="55" t="n"/>
+      <c r="R133" s="55" t="n"/>
+    </row>
+    <row r="134" ht="24.9" customHeight="1">
+      <c r="B134" s="74" t="n"/>
+      <c r="C134" s="99" t="n"/>
+      <c r="D134" s="108" t="n">
+        <v>7</v>
+      </c>
+      <c r="E134" s="302" t="n"/>
+      <c r="F134" s="187" t="n"/>
+      <c r="G134" s="187" t="n"/>
+      <c r="H134" s="187" t="n"/>
+      <c r="I134" s="187" t="n"/>
+      <c r="J134" s="187" t="n"/>
+      <c r="K134" s="187" t="n"/>
+      <c r="L134" s="187" t="n"/>
+      <c r="M134" s="187" t="n"/>
+      <c r="N134" s="187" t="n"/>
+      <c r="O134" s="187" t="n"/>
+      <c r="P134" s="188" t="n"/>
+      <c r="Q134" s="99" t="n"/>
+      <c r="R134" s="99" t="n"/>
+    </row>
+    <row r="135" ht="25.8" customHeight="1">
+      <c r="B135" s="74" t="n"/>
+      <c r="C135" s="74" t="n"/>
+      <c r="D135" s="375" t="n">
+        <v>8</v>
+      </c>
+      <c r="E135" s="376" t="n"/>
+      <c r="F135" s="187" t="n"/>
+      <c r="G135" s="187" t="n"/>
+      <c r="H135" s="187" t="n"/>
+      <c r="I135" s="187" t="n"/>
+      <c r="J135" s="187" t="n"/>
+      <c r="K135" s="187" t="n"/>
+      <c r="L135" s="187" t="n"/>
+      <c r="M135" s="187" t="n"/>
+      <c r="N135" s="187" t="n"/>
+      <c r="O135" s="187" t="n"/>
+      <c r="P135" s="188" t="n"/>
+      <c r="Q135" s="55" t="n"/>
+      <c r="R135" s="55" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="198">
+  <mergeCells count="207">
     <mergeCell ref="M61:P61"/>
     <mergeCell ref="H123:J123"/>
     <mergeCell ref="D116:F116"/>
@@ -6020,6 +6325,7 @@
     <mergeCell ref="D45:I45"/>
     <mergeCell ref="D23:H23"/>
     <mergeCell ref="L38:O38"/>
+    <mergeCell ref="E135:P135"/>
     <mergeCell ref="E51:J51"/>
     <mergeCell ref="L31:O31"/>
     <mergeCell ref="L40:O40"/>
@@ -6037,6 +6343,7 @@
     <mergeCell ref="E77:P77"/>
     <mergeCell ref="E104:M104"/>
     <mergeCell ref="E49:J49"/>
+    <mergeCell ref="E133:P133"/>
     <mergeCell ref="E80:P80"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="K63:L63"/>
@@ -6051,6 +6358,7 @@
     <mergeCell ref="D33:I33"/>
     <mergeCell ref="D42:I42"/>
     <mergeCell ref="E72:P72"/>
+    <mergeCell ref="E134:P134"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="M64:P64"/>
     <mergeCell ref="G65:H65"/>
@@ -6126,17 +6434,21 @@
     <mergeCell ref="G63:H63"/>
     <mergeCell ref="K65:L65"/>
     <mergeCell ref="I63:J63"/>
+    <mergeCell ref="E127:P127"/>
     <mergeCell ref="D14:E14"/>
+    <mergeCell ref="E129:P129"/>
     <mergeCell ref="E88:M88"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="E79:P79"/>
     <mergeCell ref="L25:O25"/>
     <mergeCell ref="E73:P73"/>
     <mergeCell ref="I65:J65"/>
+    <mergeCell ref="E131:P131"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D18:J18"/>
     <mergeCell ref="D61:F61"/>
     <mergeCell ref="F16:J16"/>
+    <mergeCell ref="E128:P128"/>
     <mergeCell ref="O116:P116"/>
     <mergeCell ref="D22:H22"/>
     <mergeCell ref="M66:P66"/>
@@ -6165,6 +6477,7 @@
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="L15:O15"/>
     <mergeCell ref="D63:F63"/>
+    <mergeCell ref="E130:P130"/>
     <mergeCell ref="E68:P68"/>
     <mergeCell ref="O122:P122"/>
     <mergeCell ref="D46:I46"/>
@@ -6172,6 +6485,7 @@
     <mergeCell ref="E111:M111"/>
     <mergeCell ref="D40:I40"/>
     <mergeCell ref="D65:F65"/>
+    <mergeCell ref="E132:P132"/>
     <mergeCell ref="N49:O49"/>
     <mergeCell ref="K62:L62"/>
     <mergeCell ref="E87:M87"/>
